--- a/templates/Capitania Prev Itau FIE - template.xlsx
+++ b/templates/Capitania Prev Itau FIE - template.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$43</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -750,7 +750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="22.28515625" customWidth="1" style="57" min="1" max="1"/>
@@ -758,8 +758,8 @@
     <col width="5.42578125" customWidth="1" style="57" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="57" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="57" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="57" min="10" max="17"/>
-    <col width="9.140625" customWidth="1" style="57" min="18" max="16384"/>
+    <col width="9.140625" customWidth="1" style="57" min="10" max="18"/>
+    <col width="9.140625" customWidth="1" style="57" min="19" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -903,20 +903,20 @@
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>1.5458477</v>
+        <v>1.5577761</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>6.857549356409365e-05</v>
+        <v>0.0001630795479563574</v>
       </c>
       <c r="E17" s="11" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.1263686200416977</v>
+        <v>0.3005175225316821</v>
       </c>
       <c r="G17" s="4" t="n"/>
     </row>
@@ -924,20 +924,20 @@
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>1.5457417</v>
+        <v>1.5575221</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>0.005512770031961267</v>
+        <v>0.0003512580033386836</v>
       </c>
       <c r="E18" s="15" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>10.15874775870274</v>
+        <v>0.6472864700423122</v>
       </c>
       <c r="G18" s="4" t="n"/>
     </row>
@@ -945,20 +945,20 @@
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>1.5372671</v>
+        <v>1.5569752</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>-4.618564469427433e-06</v>
+        <v>0.001651432358630078</v>
       </c>
       <c r="E19" s="15" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>-0.008510935732889233</v>
+        <v>3.043204174057295</v>
       </c>
       <c r="G19" s="4" t="n"/>
     </row>
@@ -966,20 +966,20 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>1.5372742</v>
+        <v>1.5544082</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>-0.00233439368585775</v>
+        <v>-0.001314077163243277</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>-4.301742406566592</v>
+        <v>-2.421537332314734</v>
       </c>
       <c r="G20" s="4" t="n"/>
     </row>
@@ -987,20 +987,20 @@
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>1.5408712</v>
+        <v>1.5564535</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0.0008929542873270524</v>
+        <v>0.002036580288511392</v>
       </c>
       <c r="E21" s="15" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>1.645506217820667</v>
+        <v>3.752941864323109</v>
       </c>
       <c r="G21" s="4" t="n"/>
     </row>
@@ -1041,18 +1041,18 @@
     <row r="24" ht="15.95" customHeight="1">
       <c r="B24" s="44" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="44" t="inlineStr"/>
       <c r="D24" s="11" t="n">
-        <v>0.006338408313148136</v>
+        <v>0.005075003372775777</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.6046156765839491</v>
+        <v>1.333833148778486</v>
       </c>
       <c r="G24" s="20" t="n"/>
     </row>
@@ -1065,13 +1065,13 @@
       </c>
       <c r="C25" s="45" t="inlineStr"/>
       <c r="D25" s="15" t="n">
-        <v>0.009489351156341641</v>
+        <v>0.01144079282903587</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>0.8181988053045181</v>
+        <v>0.9939508721024581</v>
       </c>
       <c r="G25" s="23" t="n"/>
       <c r="H25" s="24" t="n"/>
@@ -1085,13 +1085,13 @@
       </c>
       <c r="C26" s="45" t="inlineStr"/>
       <c r="D26" s="15" t="n">
-        <v>0.03900531988184008</v>
+        <v>0.04062800171307446</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>1.105338007426537</v>
+        <v>1.1542486672588</v>
       </c>
       <c r="G26" s="23" t="n"/>
     </row>
@@ -1104,13 +1104,13 @@
       </c>
       <c r="C27" s="45" t="inlineStr"/>
       <c r="D27" s="15" t="n">
-        <v>0.08382737289907993</v>
+        <v>0.08642133820596176</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>1.166409901135233</v>
+        <v>1.204055568258396</v>
       </c>
       <c r="G27" s="23" t="n"/>
     </row>
@@ -1123,13 +1123,13 @@
       </c>
       <c r="C28" s="45" t="inlineStr"/>
       <c r="D28" s="15" t="n">
-        <v>0.173591246181372</v>
+        <v>0.176689453005499</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>1.174366358188062</v>
+        <v>1.19371831233138</v>
       </c>
       <c r="G28" s="23" t="n"/>
     </row>
@@ -1137,18 +1137,18 @@
       <c r="A29" s="25" t="n"/>
       <c r="B29" s="45" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C29" s="45" t="inlineStr"/>
       <c r="D29" s="15" t="n">
-        <v>0.0346201545925664</v>
+        <v>0.2939470292587028</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>1.067237831665872</v>
+        <v>1.057627939595925</v>
       </c>
       <c r="G29" s="23" t="n"/>
     </row>
@@ -1156,18 +1156,18 @@
       <c r="A30" s="25" t="n"/>
       <c r="B30" s="45" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C30" s="45" t="inlineStr"/>
       <c r="D30" s="15" t="n">
-        <v>0.1752175038167878</v>
+        <v>0.04260371147986008</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>1.224160804586991</v>
+        <v>1.119518625112608</v>
       </c>
       <c r="G30" s="23" t="n"/>
     </row>
@@ -1175,18 +1175,18 @@
       <c r="A31" s="25" t="n"/>
       <c r="B31" s="45" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C31" s="45" t="inlineStr"/>
-      <c r="D31" s="26" t="n">
-        <v>0.09683592594752621</v>
-      </c>
-      <c r="E31" s="26" t="n">
-        <v>0.1092049264357533</v>
+      <c r="D31" s="15" t="n">
+        <v>0.1752175038167878</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.143132751155109</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>0.8867358745440488</v>
+        <v>1.224160804586991</v>
       </c>
       <c r="G31" s="23" t="n"/>
     </row>
@@ -1194,164 +1194,183 @@
       <c r="A32" s="25" t="n"/>
       <c r="B32" s="45" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C32" s="45" t="inlineStr"/>
       <c r="D32" s="26" t="n">
-        <v>0.5458476999999999</v>
+        <v>0.09683592594752621</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>0.5202703393664174</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>1.049161673649762</v>
+        <v>0.8867358745440488</v>
       </c>
       <c r="G32" s="23" t="n"/>
     </row>
     <row r="33" ht="15.95" customHeight="1">
       <c r="A33" s="25" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="26.1" customHeight="1">
+      <c r="B33" s="45" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C33" s="45" t="inlineStr"/>
+      <c r="D33" s="26" t="n">
+        <v>0.5577761000000001</v>
+      </c>
+      <c r="E33" s="26" t="n">
+        <v>0.5285404496286485</v>
+      </c>
+      <c r="F33" s="22" t="n">
+        <v>1.055313931775501</v>
+      </c>
+      <c r="G33" s="23" t="n"/>
+    </row>
+    <row r="34" ht="15.95" customHeight="1">
       <c r="A34" s="25" t="n"/>
-      <c r="B34" s="42" t="inlineStr">
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="26.1" customHeight="1">
+      <c r="A35" s="25" t="n"/>
+      <c r="B35" s="42" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C34" s="42" t="n"/>
-      <c r="D34" s="42" t="n"/>
-      <c r="E34" s="42" t="n"/>
-      <c r="F34" s="42" t="n"/>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="A35" s="27" t="n"/>
-      <c r="B35" s="28" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="29" t="n"/>
-      <c r="E35" s="46" t="n">
-        <v>211991239.52</v>
-      </c>
-      <c r="F35" s="46" t="n"/>
+      <c r="C35" s="42" t="n"/>
+      <c r="D35" s="42" t="n"/>
+      <c r="E35" s="42" t="n"/>
+      <c r="F35" s="42" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="27" t="n"/>
-      <c r="B36" s="30" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C36" s="29" t="n"/>
       <c r="D36" s="29" t="n"/>
       <c r="E36" s="46" t="n">
-        <v>98243922.77388889</v>
+        <v>231433542.35</v>
       </c>
       <c r="F36" s="46" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="27" t="n"/>
-      <c r="B37" s="31" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="46" t="n">
+        <v>104838543.5531349</v>
+      </c>
+      <c r="F37" s="46" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
-      <c r="A38" s="32" t="n"/>
-      <c r="B38" s="33" t="inlineStr">
+      <c r="A38" s="27" t="n"/>
+      <c r="B38" s="31" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="15.95" customHeight="1">
+      <c r="A39" s="32" t="n"/>
+      <c r="B39" s="33" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D38" s="35" t="n"/>
-      <c r="E38" s="35" t="n"/>
-      <c r="F38" s="35" t="n"/>
-      <c r="G38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="34" t="inlineStr">
+      <c r="C39" s="34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="n"/>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="35" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="B40" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="D39" s="36" t="n"/>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="36" t="n"/>
-      <c r="G39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="15.95" customHeight="1">
-      <c r="B40" s="37" t="n"/>
-      <c r="C40" s="38" t="n"/>
       <c r="D40" s="36" t="n"/>
       <c r="E40" s="36" t="n"/>
       <c r="F40" s="36" t="n"/>
       <c r="G40" s="4" t="n"/>
     </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="56" t="inlineStr">
+    <row r="41" ht="15.95" customHeight="1">
+      <c r="B41" s="37" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="36" t="n"/>
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="36" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="48" customHeight="1">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="56" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="58" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="39" t="n"/>
-      <c r="C43" s="39" t="n"/>
-      <c r="D43" s="39" t="n"/>
-      <c r="E43" s="39" t="n"/>
-      <c r="F43" s="39" t="n"/>
+      <c r="B43" s="58" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="40" t="n"/>
-      <c r="C44" s="41" t="n"/>
-      <c r="D44" s="23" t="n"/>
-      <c r="E44" s="23" t="n"/>
-      <c r="F44" s="23" t="n"/>
+      <c r="B44" s="39" t="n"/>
+      <c r="C44" s="39" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
       <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="4" t="n"/>
       <c r="B45" s="40" t="n"/>
       <c r="C45" s="41" t="n"/>
       <c r="D45" s="23" t="n"/>
       <c r="E45" s="23" t="n"/>
       <c r="F45" s="23" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="40" t="n"/>
+      <c r="C46" s="41" t="n"/>
+      <c r="D46" s="23" t="n"/>
+      <c r="E46" s="23" t="n"/>
+      <c r="F46" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B42:F42"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="86" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="84"/>
 </worksheet>
 </file>